--- a/dataset/Faulty/race_condition.xlsx
+++ b/dataset/Faulty/race_condition.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/race_condition.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/race_condition.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>int race_glb_1=5; int race_glb_2=3; int race_condition_002_gbl=0; int instance1=0; int x=0; int race_condition_005_glb_data = 0; pthread_mutex_t race_condition_006_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_006_glb_data = 0; pthread_mutex_t race_condition_007_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float race_condition_007_glb_data = 1000.0; pthread_mutex_t race_condition_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t race_condition_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; float race_condition_008_glb_data = 1000.0; extern volatile int vflag; void race_condition_008 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, race_condition_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, race_condition_008_tsk_002, (void *)t2); sleep(1); #endif /* defined(CHECKER_POLYSPACE) */ } void * race_condition_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; ip = (long)input; ip = ip *20; race_condition_008_glb_data--; #if defined PRINT_DEBUG printf("Task4_2! race condition, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void *race_condition_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; ip = (long)input; ip = ip *10; race_condition_008_glb_data++; /*Tool should detect this line as error*/ /*ERROR:Race condition*/ #if defined PRINT_DEBUG printf("Task4_1! race condition, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
+          <t>int race_glb_1=5; int race_glb_2=3; int race_condition_002_gbl=0; int instance1=0; int x=0; int race_condition_005_glb_data = 0; pthread_mutex_t race_condition_006_glb_mutex = PTHREAD_MUTEX_INITIALIZER; int race_condition_006_glb_data = 0; pthread_mutex_t race_condition_007_glb_mutex = PTHREAD_MUTEX_INITIALIZER; float race_condition_007_glb_data = 1000.0; pthread_mutex_t race_condition_008_glb_mutex_1 = PTHREAD_MUTEX_INITIALIZER; pthread_mutex_t race_condition_008_glb_mutex_2 = PTHREAD_MUTEX_INITIALIZER; float race_condition_008_glb_data = 1000.0; extern volatile int vflag; void race_condition_008 () { #if ! defined(CHECKER_POLYSPACE) pthread_t th1,th2; intptr_t t1 = 10; intptr_t t2 = 20; pthread_create(&amp;th1, NULL, race_condition_008_tsk_001, (void *)t1); pthread_create(&amp;th2, NULL, race_condition_008_tsk_002, (void *)t2); sleep(1); #endif /* defined(CHECKER_POLYSPACE) */ } void *race_condition_008_tsk_001(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; ip = (long)input; ip = ip *10; race_condition_008_glb_data++; /*Tool should detect this line as error*/ /*ERROR:Race condition*/ #if defined PRINT_DEBUG printf("Task4_1! race condition, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; } void * race_condition_008_tsk_002(void *input) { #if ! defined(CHECKER_POLYSPACE) long ip; ip = (long)input; ip = ip *20; race_condition_008_glb_data--; #if defined PRINT_DEBUG printf("Task4_2! race condition, thread #%ld!\n",ip); #endif /* defined(PRINT_DEBUG) */ #endif /* defined(CHECKER_POLYSPACE) */ return NULL; }</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
